--- a/data/trans_dic/P56$nadie-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 90,27</t>
+          <t>0,0; 89,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,59</t>
+          <t>0,0; 53,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,31</t>
+          <t>0,0; 42,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,45; 80,85</t>
+          <t>12,35; 80,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,8</t>
+          <t>0,0; 30,63</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,27</t>
+          <t>0,0; 41,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 39,84</t>
+          <t>2,05; 42,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,25</t>
+          <t>0,0; 74,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 31,41</t>
+          <t>4,59; 31,25</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,56</t>
+          <t>0,0; 56,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,07</t>
+          <t>0,0; 59,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,8</t>
+          <t>0,0; 64,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,81</t>
+          <t>0,0; 33,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,02</t>
+          <t>0,0; 33,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,5</t>
+          <t>0,0; 30,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,67</t>
+          <t>0,0; 18,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,92</t>
+          <t>0,0; 11,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 21,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 10,95</t>
+          <t>1,17; 9,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 40,19</t>
+          <t>5,32; 45,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 43,17</t>
+          <t>0,0; 41,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>0,0; 12,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,92</t>
+          <t>0,0; 14,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,95</t>
+          <t>1,61; 15,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 24,12</t>
+          <t>4,71; 24,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,43</t>
+          <t>1,59; 9,11</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,98</t>
+          <t>0,0; 37,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,09</t>
+          <t>0,0; 15,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 25,16</t>
+          <t>2,45; 25,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,94</t>
+          <t>0,0; 30,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 15,07</t>
+          <t>1,6; 14,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 36,22</t>
+          <t>7,15; 35,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,37</t>
+          <t>3,24; 10,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,9</t>
+          <t>0,0; 22,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,11</t>
+          <t>1,27; 11,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 22,95</t>
+          <t>5,04; 23,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,57</t>
+          <t>3,91; 11,22</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 26,62</t>
+          <t>6,99; 26,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,3</t>
+          <t>2,7; 13,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,95; 21,17</t>
+          <t>5,8; 20,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,77</t>
+          <t>1,23; 5,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 26,62</t>
+          <t>6,99; 26,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,3</t>
+          <t>2,7; 13,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,95; 21,17</t>
+          <t>5,8; 20,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,88</t>
+          <t>1,13; 5,75</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 16,29</t>
+          <t>1,92; 15,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 18,46</t>
+          <t>2,62; 17,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,5</t>
+          <t>2,78; 9,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 20,21</t>
+          <t>5,12; 19,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,42</t>
+          <t>3,6; 11,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,15; 22,83</t>
+          <t>11,41; 23,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,43</t>
+          <t>2,93; 6,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 15,49</t>
+          <t>5,49; 14,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,64</t>
+          <t>3,27; 8,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 19,48</t>
+          <t>9,9; 19,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,51</t>
+          <t>3,39; 6,59</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5852</t>
+          <t>0; 5829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2551</t>
+          <t>0; 3034</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2528</t>
+          <t>0; 2462</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1351</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1977</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1755; 9188</t>
+          <t>1404; 9169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3676</t>
+          <t>0; 3540</t>
         </is>
       </c>
     </row>
@@ -2135,32 +2135,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1483</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1442</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1475</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>165; 3230</t>
+          <t>166; 3415</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1474</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7508</t>
+          <t>0; 6973</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>805; 5296</t>
+          <t>775; 5269</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3508</t>
+          <t>0; 3374</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4191</t>
+          <t>0; 4255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1513</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1797</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5873</t>
+          <t>0; 4693</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 3525</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5641</t>
+          <t>0; 5841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5399</t>
+          <t>0; 5325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 996</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5795</t>
+          <t>0; 5338</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 4711</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5269</t>
+          <t>0; 5374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>738; 5536</t>
+          <t>592; 4772</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>970; 7321</t>
+          <t>969; 8376</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1144; 9436</t>
+          <t>0; 9078</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3522</t>
+          <t>0; 3637</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6230</t>
+          <t>0; 5341</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1006; 9683</t>
+          <t>980; 9278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2149; 11218</t>
+          <t>2189; 11531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1244; 6637</t>
+          <t>1249; 7172</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5325</t>
+          <t>0; 3823</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4131</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>468; 4566</t>
+          <t>445; 4627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5686</t>
+          <t>0; 5347</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1061; 9848</t>
+          <t>1045; 9315</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2940; 12956</t>
+          <t>2559; 12862</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2675; 8592</t>
+          <t>2684; 8563</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5748</t>
+          <t>0; 6324</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1061; 9276</t>
+          <t>1064; 9307</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3189; 14101</t>
+          <t>3095; 14266</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4003; 11680</t>
+          <t>3947; 11335</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4355; 15952</t>
+          <t>4192; 15727</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2872; 12748</t>
+          <t>2801; 13664</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5732; 20385</t>
+          <t>5583; 20043</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1180; 5958</t>
+          <t>1270; 5879</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4355; 15952</t>
+          <t>4192; 15727</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2872; 12748</t>
+          <t>2801; 13664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5732; 20385</t>
+          <t>5583; 20043</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1267; 6196</t>
+          <t>1191; 6055</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>928; 7867</t>
+          <t>929; 7709</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>0; 7218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1821; 13312</t>
+          <t>1886; 12832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2955; 10401</t>
+          <t>2754; 9656</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5358; 18907</t>
+          <t>4787; 18084</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7230; 21280</t>
+          <t>7349; 22666</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19013; 38942</t>
+          <t>19467; 39556</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6858; 15838</t>
+          <t>7218; 16249</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7614; 21970</t>
+          <t>7792; 21243</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8616; 24439</t>
+          <t>9236; 25323</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23568; 47263</t>
+          <t>24025; 47482</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11755; 22475</t>
+          <t>11700; 22759</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$nadie-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 89,91</t>
+          <t>0,0; 89,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,03</t>
+          <t>0,0; 42,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,18</t>
+          <t>0,0; 39,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,35; 80,68</t>
+          <t>16,86; 82,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,63</t>
+          <t>0,0; 30,04</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,26</t>
+          <t>0,0; 40,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 42,12</t>
+          <t>4,32; 41,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,53</t>
+          <t>0,0; 75,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 31,25</t>
+          <t>5,73; 33,32</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,31</t>
+          <t>0,0; 56,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,98</t>
+          <t>0,0; 58,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,57</t>
+          <t>0,0; 65,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,69</t>
+          <t>0,0; 37,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,16</t>
+          <t>0,0; 29,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,09</t>
+          <t>0,0; 29,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1084,47 +1084,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>4,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,12</t>
+          <t>0,0; 20,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,08</t>
+          <t>0,0; 11,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,79</t>
+          <t>0,0; 21,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,44</t>
+          <t>1,41; 12,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 45,99</t>
+          <t>5,22; 40,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,53</t>
+          <t>5,41; 42,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,9</t>
+          <t>0,0; 13,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,51</t>
+          <t>0,0; 14,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 15,28</t>
+          <t>1,62; 15,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 24,79</t>
+          <t>4,55; 25,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,11</t>
+          <t>1,53; 8,6</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,32</t>
+          <t>0,0; 35,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,59 +1287,59 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,25</t>
+          <t>0,0; 13,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 25,49</t>
+          <t>2,54; 25,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,98</t>
+          <t>0,0; 32,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,25</t>
+          <t>1,62; 13,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 35,96</t>
+          <t>7,35; 38,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 10,34</t>
+          <t>3,0; 10,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,99</t>
+          <t>0,0; 23,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,15</t>
+          <t>1,27; 9,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 23,22</t>
+          <t>5,35; 23,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 11,22</t>
+          <t>3,66; 10,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 26,24</t>
+          <t>7,16; 27,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 13,19</t>
+          <t>2,87; 13,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,81</t>
+          <t>5,72; 20,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,7</t>
+          <t>1,23; 5,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 26,24</t>
+          <t>7,16; 27,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 13,19</t>
+          <t>2,87; 13,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,81</t>
+          <t>5,72; 20,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,75</t>
+          <t>1,22; 5,25</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 15,97</t>
+          <t>1,93; 16,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 17,8</t>
+          <t>3,2; 16,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,75</t>
+          <t>2,86; 11,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 19,33</t>
+          <t>4,9; 18,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,1</t>
+          <t>3,53; 10,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,41; 23,19</t>
+          <t>10,96; 24,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,6</t>
+          <t>2,96; 6,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,98</t>
+          <t>5,42; 15,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,96</t>
+          <t>3,11; 8,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,9; 19,57</t>
+          <t>9,96; 19,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,59</t>
+          <t>3,4; 6,71</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>610</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1220</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5829</t>
+          <t>0; 5804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3034</t>
+          <t>0; 2497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2462</t>
+          <t>0; 2521</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1404; 9169</t>
+          <t>1917; 9341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>0; 3695</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2861</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>0; 3658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>166; 3415</t>
+          <t>418; 4038</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6973</t>
+          <t>0; 7096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>775; 5269</t>
+          <t>1067; 6205</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3374</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4255</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4693</t>
+          <t>0; 4734</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3525</t>
+          <t>0; 3950</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5841</t>
+          <t>0; 5255</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5325</t>
+          <t>0; 5247</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3512</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5338</t>
+          <t>0; 5951</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4711</t>
+          <t>0; 4969</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5374</t>
+          <t>0; 5329</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>592; 4772</t>
+          <t>773; 6575</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>969; 8376</t>
+          <t>952; 7405</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 9078</t>
+          <t>1183; 9251</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3637</t>
+          <t>0; 3934</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5341</t>
+          <t>0; 5300</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>980; 9278</t>
+          <t>984; 9163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2189; 11531</t>
+          <t>2116; 11779</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1249; 7172</t>
+          <t>1297; 7292</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7215</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 3625</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2769,59 +2769,59 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>0; 3591</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>445; 4627</t>
+          <t>476; 4839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5347</t>
+          <t>0; 5675</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1045; 9315</t>
+          <t>1056; 8973</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2559; 12862</t>
+          <t>2628; 13819</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2684; 8563</t>
+          <t>2699; 9183</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6324</t>
+          <t>0; 6356</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1064; 9307</t>
+          <t>1061; 8264</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3095; 14266</t>
+          <t>3288; 14293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3947; 11335</t>
+          <t>3976; 11464</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3108</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4192; 15727</t>
+          <t>4290; 16586</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2801; 13664</t>
+          <t>2969; 13610</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5583; 20043</t>
+          <t>5506; 19957</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1270; 5879</t>
+          <t>1391; 6457</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4192; 15727</t>
+          <t>4290; 16586</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2801; 13664</t>
+          <t>2969; 13610</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5583; 20043</t>
+          <t>5506; 19957</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1191; 6055</t>
+          <t>1408; 6040</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>17918</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>929; 7709</t>
+          <t>930; 7811</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7218</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1886; 12832</t>
+          <t>2310; 12109</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2754; 9656</t>
+          <t>2997; 11524</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4787; 18084</t>
+          <t>4581; 17262</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7349; 22666</t>
+          <t>7210; 22091</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19467; 39556</t>
+          <t>18698; 41211</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7218; 16249</t>
+          <t>7978; 17277</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7792; 21243</t>
+          <t>7687; 21536</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9236; 25323</t>
+          <t>8801; 23865</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24025; 47482</t>
+          <t>24173; 47392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11700; 22759</t>
+          <t>12736; 25118</t>
         </is>
       </c>
     </row>
